--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.43808087632218</v>
+        <v>2.508688142402355</v>
       </c>
       <c r="D2" t="n">
-        <v>24.16659525256401</v>
+        <v>3.927071728541652</v>
       </c>
       <c r="E2" t="n">
-        <v>11.85714624502763</v>
+        <v>1.926786264816989</v>
       </c>
       <c r="F2" t="n">
-        <v>7.718738263787949</v>
+        <v>1.254294967865542</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.0063665385237</v>
+        <v>1.788534562510101</v>
       </c>
       <c r="D3" t="n">
-        <v>11.60014771493965</v>
+        <v>1.885024003677693</v>
       </c>
       <c r="E3" t="n">
-        <v>11.85714624502763</v>
+        <v>1.926786264816989</v>
       </c>
       <c r="F3" t="n">
-        <v>7.718738263787949</v>
+        <v>1.254294967865542</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.04383457876554</v>
+        <v>2.119623119049401</v>
       </c>
       <c r="D4" t="n">
-        <v>13.04376137149994</v>
+        <v>2.11961122286874</v>
       </c>
       <c r="E4" t="n">
-        <v>11.85714624502763</v>
+        <v>1.926786264816989</v>
       </c>
       <c r="F4" t="n">
-        <v>7.718738263787949</v>
+        <v>1.254294967865542</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.49777101244603</v>
+        <v>4.143387789522481</v>
       </c>
       <c r="D5" t="n">
-        <v>24.80898513755098</v>
+        <v>4.031460084852034</v>
       </c>
       <c r="E5" t="n">
-        <v>11.85714624502763</v>
+        <v>1.926786264816989</v>
       </c>
       <c r="F5" t="n">
-        <v>7.718738263787949</v>
+        <v>1.254294967865542</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.81839575042655</v>
+        <v>4.195489309444315</v>
       </c>
       <c r="D6" t="n">
-        <v>25.50493382132093</v>
+        <v>4.144551745964652</v>
       </c>
       <c r="E6" t="n">
-        <v>11.85714624502763</v>
+        <v>1.926786264816989</v>
       </c>
       <c r="F6" t="n">
-        <v>7.718738263787949</v>
+        <v>1.254294967865542</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.70644871623161</v>
+        <v>7.102297916387637</v>
       </c>
       <c r="D7" t="n">
-        <v>26.18922942538818</v>
+        <v>4.25574978162558</v>
       </c>
       <c r="E7" t="n">
-        <v>11.85714624502763</v>
+        <v>1.926786264816989</v>
       </c>
       <c r="F7" t="n">
-        <v>7.718738263787949</v>
+        <v>1.254294967865542</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.25864549067764</v>
+        <v>6.379529892235116</v>
       </c>
       <c r="D8" t="n">
-        <v>35.91888533530987</v>
+        <v>5.836818866987855</v>
       </c>
       <c r="E8" t="n">
-        <v>11.85714624502763</v>
+        <v>1.926786264816989</v>
       </c>
       <c r="F8" t="n">
-        <v>7.718738263787949</v>
+        <v>1.254294967865542</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
